--- a/data/trans_bre/IP19C02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 39,93</t>
+          <t>-50,09; 39,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-85,72; 346,53</t>
+          <t>-86,03; 392,23</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 4,57</t>
+          <t>-3,95; 4,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 4,22</t>
+          <t>-5,77; 4,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 10,24</t>
+          <t>-6,12; 9,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,84; -1,64</t>
+          <t>-27,33; -2,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,44; 462,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 415,55</t>
+          <t>-89,07; 437,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,06; 195,98</t>
+          <t>-46,88; 161,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,49; -5,01</t>
+          <t>-64,35; -7,29</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 5,16</t>
+          <t>-6,81; 5,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 1,98</t>
+          <t>-6,73; 2,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 7,51</t>
+          <t>-7,01; 7,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 18,24</t>
+          <t>-1,29; 18,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,14; 104,2</t>
+          <t>-62,14; 96,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-81,82; 78,02</t>
+          <t>-79,05; 83,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 52,62</t>
+          <t>-31,31; 52,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 105,74</t>
+          <t>-4,74; 105,09</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 7,38</t>
+          <t>-2,71; 6,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 5,76</t>
+          <t>-5,19; 5,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 5,56</t>
+          <t>-12,07; 5,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 4,95</t>
+          <t>-12,58; 4,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,73; 137,6</t>
+          <t>-31,78; 125,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,58; 94,15</t>
+          <t>-46,19; 91,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 25,49</t>
+          <t>-38,6; 24,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,85; 16,07</t>
+          <t>-30,86; 15,21</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,07</t>
+          <t>-2,55; 3,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,05</t>
+          <t>-3,59; 2,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,28</t>
+          <t>-5,43; 4,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 3,65</t>
+          <t>-7,81; 3,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 77,58</t>
+          <t>-30,53; 69,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 44,06</t>
+          <t>-46,43; 50,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 24,11</t>
+          <t>-25,77; 23,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 13,52</t>
+          <t>-22,44; 13,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Edad-trans_bre.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 39,96</t>
+          <t>-47,7; 40,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-86,03; 392,23</t>
+          <t>-79,0; 409,18</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 4,85</t>
+          <t>-3,76; 5,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 4,27</t>
+          <t>-5,45; 4,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 9,91</t>
+          <t>-6,75; 9,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,33; -2,15</t>
+          <t>-28,06; -2,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,96; 610,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,07; 437,43</t>
+          <t>-89,02; 453,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,88; 161,33</t>
+          <t>-49,62; 145,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,35; -7,29</t>
+          <t>-64,71; -5,48</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 5,14</t>
+          <t>-6,98; 5,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 2,1</t>
+          <t>-7,29; 1,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 7,57</t>
+          <t>-7,57; 7,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 18,06</t>
+          <t>-0,85; 18,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,14; 96,66</t>
+          <t>-65,26; 107,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-79,05; 83,9</t>
+          <t>-84,82; 56,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 52,6</t>
+          <t>-34,77; 54,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 105,09</t>
+          <t>-2,68; 104,13</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 6,59</t>
+          <t>-2,76; 7,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 5,49</t>
+          <t>-5,65; 5,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 5,28</t>
+          <t>-13,07; 4,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 4,66</t>
+          <t>-12,63; 5,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 125,69</t>
+          <t>-30,82; 142,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,19; 91,49</t>
+          <t>-50,41; 92,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,6; 24,09</t>
+          <t>-40,58; 20,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 15,21</t>
+          <t>-30,7; 17,2</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,63</t>
+          <t>-2,48; 3,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 2,42</t>
+          <t>-3,58; 2,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 4,1</t>
+          <t>-5,4; 4,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 3,82</t>
+          <t>-7,65; 4,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 69,16</t>
+          <t>-31,15; 75,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 50,32</t>
+          <t>-45,53; 46,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 23,68</t>
+          <t>-24,55; 26,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 13,13</t>
+          <t>-22,3; 15,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,52</t>
+          <t>-4,61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-12,43%</t>
+          <t>-12,7%</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-47,7; 40,95</t>
+          <t>-51,57; 38,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-79,0; 409,18</t>
+          <t>-85,92; 341,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-15,27</t>
+          <t>-14,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-42,44%</t>
+          <t>-39,3%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 5,18</t>
+          <t>-4,55; 4,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 4,36</t>
+          <t>-5,89; 4,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 9,84</t>
+          <t>-5,96; 10,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,06; -2,57</t>
+          <t>-27,45; -0,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,96; 610,17</t>
+          <t>-86,44; 462,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,02; 453,04</t>
+          <t>-100,0; 415,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 145,44</t>
+          <t>-46,06; 195,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,71; -5,48</t>
+          <t>-64,78; -1,04</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,42</t>
+          <t>8,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 5,36</t>
+          <t>-7,08; 5,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 1,58</t>
+          <t>-6,87; 1,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 7,49</t>
+          <t>-7,24; 7,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 18,07</t>
+          <t>-1,16; 18,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,26; 107,31</t>
+          <t>-61,14; 104,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-84,82; 56,94</t>
+          <t>-81,82; 78,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,77; 54,66</t>
+          <t>-32,62; 52,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 104,13</t>
+          <t>-4,36; 93,2</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,3</t>
+          <t>-5,59</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-11,74%</t>
+          <t>-14,25%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 7,21</t>
+          <t>-2,53; 7,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 5,33</t>
+          <t>-5,1; 5,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 4,78</t>
+          <t>-11,64; 5,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 5,3</t>
+          <t>-14,51; 2,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,82; 142,73</t>
+          <t>-28,73; 137,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 92,58</t>
+          <t>-46,58; 94,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,58; 20,46</t>
+          <t>-37,71; 25,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,7; 17,2</t>
+          <t>-32,47; 8,83</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-5,64%</t>
+          <t>-6,99%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,83</t>
+          <t>-2,18; 4,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,19</t>
+          <t>-3,45; 2,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,63</t>
+          <t>-5,33; 4,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 4,39</t>
+          <t>-8,31; 2,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 75,54</t>
+          <t>-28,06; 77,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,53; 46,43</t>
+          <t>-43,59; 44,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 26,7</t>
+          <t>-24,63; 24,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,3; 15,02</t>
+          <t>-22,64; 10,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,173 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19,02</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-12,7%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>19.01884580258737</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-4.614168040785405</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="n">
+        <v>-0.1270406023785841</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-51,57; 38,42</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-85,92; 341,68</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>-51.57124545701402</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-0.859173829579855</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>38.42494264193056</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>3.416828844099829</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-14,13</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,4%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-10,69%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-39,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,55; 4,57</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,89; 4,22</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,96; 10,24</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-27,45; -0,42</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-86,44; 462,4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 415,55</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-46,06; 195,98</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-64,78; -1,04</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.3844366581418353</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.4011089686061086</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.510221914612865</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-14.12920721295013</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.123968944479413</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1069164411099285</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.1461567290076005</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.3930187946952265</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,1</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-11,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-38,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33,21%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.553929912038406</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.88952311031947</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.956080788748688</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-27.44727161903292</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.8643618373369215</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4606023986467323</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6477559383758552</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,08; 5,16</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,87; 1,98</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,24; 7,51</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,16; 18,21</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-61,14; 104,2</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-81,82; 78,02</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-32,62; 52,62</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-4,36; 93,2</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.569099051048758</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.216084198585693</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>10.23599135489769</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-0.4191644480276509</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>4.624047435683055</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4.155487686761005</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.959800880222982</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>-0.01036388257546489</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +793,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,69</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-5,59</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-13,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-14,25%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.9201524734941818</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.233149586833928</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.02768186642312376</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>8.10015545848495</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1117383721668307</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.3843515254988165</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.001533614942263997</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.332096651916529</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,53; 7,38</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,1; 5,76</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-11,64; 5,56</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-14,51; 2,94</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-28,73; 137,6</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-46,58; 94,15</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-37,71; 25,49</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-32,47; 8,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.080240258913752</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.865859809102172</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.243917544782266</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.161547425208516</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.611419843644603</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.818216137402794</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3261788932580038</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.04359426624019819</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.159144080883712</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.979261658752536</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.514451879273949</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>18.20626586588378</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.041956010190843</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.7802105311928016</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.5262300332900971</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.9320160856639599</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.057688806703686</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.01506955216074857</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-3.691912635630246</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-5.587783123476248</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.2761792629557424</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.001760805544457132</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1368228896149122</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1425050168137578</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.533874163224643</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.103530759629563</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-11.63641516019045</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-14.50946230036919</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2873335952263618</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4658430926215945</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3770880751454371</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3246702168794836</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.377184383524982</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.76069282603379</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.561369500522153</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.942066008097876</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.375966942830612</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.9415245823530076</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.2549303843426968</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.0883400260085221</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,36</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-9,11%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-2,97%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-6,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,18; 4,07</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,45; 2,05</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-5,33; 4,28</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-8,31; 2,95</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-28,06; 77,58</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-43,59; 44,06</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-24,63; 24,11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-22,64; 10,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.6611939300429026</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.5777745524376786</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.5809774516852995</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-2.356307878525499</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.09907249671699263</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.09110525685313917</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.02972046326396993</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.06989419700704971</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.17772021726706</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.453172613381513</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.331072946638328</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-8.306906683862545</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2805663234190969</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.435860963293157</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2462828515585462</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.226380468656766</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4.068503744071744</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.051364992515159</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.276837228951448</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.94573267037387</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.7757620599852281</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.44057784555687</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.2410626470452018</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1019280319824159</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1091,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
